--- a/data/trans_dic/P19C09-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C09-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos (tasa de respuesta: 99,04%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,11</t>
+          <t>0,88; 5,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,0</t>
+          <t>0,38; 4,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,8</t>
+          <t>2,54; 8,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,74</t>
+          <t>1,11; 7,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 11,48</t>
+          <t>4,35; 12,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 8,43</t>
+          <t>2,34; 8,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,93</t>
+          <t>1,58; 5,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,11</t>
+          <t>2,87; 7,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,72</t>
+          <t>2,94; 6,67</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,83</t>
+          <t>1,77; 5,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,76</t>
+          <t>0,49; 2,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,9</t>
+          <t>1,24; 4,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,45</t>
+          <t>2,02; 5,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,59</t>
+          <t>0,99; 4,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,15</t>
+          <t>0,51; 3,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,86</t>
+          <t>2,32; 4,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,94</t>
+          <t>0,98; 3,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,29</t>
+          <t>1,17; 3,27</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,23</t>
+          <t>0,74; 4,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,75</t>
+          <t>0,34; 3,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,15</t>
+          <t>0,27; 3,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 6,56</t>
+          <t>2,05; 6,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,23</t>
+          <t>1,3; 5,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,05</t>
+          <t>0,3; 3,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,64</t>
+          <t>1,66; 4,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,69</t>
+          <t>1,3; 3,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,43</t>
+          <t>0,46; 2,52</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 7,01</t>
+          <t>1,63; 6,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,2</t>
+          <t>1,64; 6,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 10,26</t>
+          <t>4,5; 10,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,54</t>
+          <t>1,65; 5,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,8</t>
+          <t>2,08; 6,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 7,77</t>
+          <t>3,2; 8,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,13</t>
+          <t>2,05; 5,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,54</t>
+          <t>2,3; 5,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,01</t>
+          <t>4,26; 8,01</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,36</t>
+          <t>1,48; 7,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,27</t>
+          <t>0,63; 5,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 8,65</t>
+          <t>1,6; 8,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,59</t>
+          <t>1,1; 6,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,55</t>
+          <t>0,59; 6,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 8,83</t>
+          <t>1,93; 9,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,54</t>
+          <t>1,6; 5,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,55</t>
+          <t>0,84; 4,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,26</t>
+          <t>2,44; 7,01</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,12</t>
+          <t>0,55; 5,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,95</t>
+          <t>0,39; 3,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,45</t>
+          <t>1,04; 6,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,43</t>
+          <t>1,47; 6,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,88</t>
+          <t>0,76; 4,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,2</t>
+          <t>1,09; 4,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,19</t>
+          <t>1,32; 4,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,0</t>
+          <t>0,7; 3,29</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,22</t>
+          <t>1,2; 4,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,03</t>
+          <t>1,34; 4,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,42</t>
+          <t>1,02; 4,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,4</t>
+          <t>2,87; 6,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,66</t>
+          <t>1,11; 3,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,97</t>
+          <t>1,61; 4,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,78</t>
+          <t>2,41; 4,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,22</t>
+          <t>1,51; 3,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,84</t>
+          <t>1,7; 3,95</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,67</t>
+          <t>1,13; 3,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,19</t>
+          <t>0,17; 1,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,43</t>
+          <t>1,12; 3,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,06</t>
+          <t>0,77; 3,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,28</t>
+          <t>0,55; 2,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,94</t>
+          <t>0,78; 2,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,88</t>
+          <t>1,19; 3,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,76</t>
+          <t>0,57; 1,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,77</t>
+          <t>1,14; 2,69</t>
         </is>
       </c>
     </row>
@@ -1563,42 +1563,42 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,33</t>
+          <t>1,22; 2,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,3; 3,64</t>
+          <t>2,31; 3,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,9</t>
+          <t>2,51; 3,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,48</t>
+          <t>2,17; 3,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,34</t>
+          <t>2,09; 3,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,43</t>
+          <t>2,45; 3,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,76</t>
+          <t>1,88; 2,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,2</t>
+          <t>2,35; 3,24</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos (tasa de respuesta: 99,04%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1607; 9776</t>
+          <t>1688; 10549</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>933; 12481</t>
+          <t>939; 11396</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5849; 19117</t>
+          <t>6230; 19968</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2345; 13572</t>
+          <t>2234; 14329</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11494; 28624</t>
+          <t>10847; 30189</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5604; 20759</t>
+          <t>5773; 20074</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6203; 19346</t>
+          <t>6219; 20824</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14609; 35491</t>
+          <t>14315; 36219</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14184; 33030</t>
+          <t>14464; 32787</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6992; 23834</t>
+          <t>7229; 23442</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1880; 10895</t>
+          <t>1939; 11174</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4864; 17806</t>
+          <t>4493; 17209</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8628; 24043</t>
+          <t>8902; 24459</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4151; 18904</t>
+          <t>4075; 17146</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1981; 12405</t>
+          <t>2010; 11877</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19693; 41320</t>
+          <t>19679; 41960</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7232; 23704</t>
+          <t>7899; 24413</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8392; 24926</t>
+          <t>8824; 24700</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1821; 10016</t>
+          <t>1754; 10273</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1014; 10963</t>
+          <t>1009; 9201</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>787; 9142</t>
+          <t>783; 8781</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5958; 18958</t>
+          <t>5920; 19427</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5086; 17185</t>
+          <t>4282; 16941</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>927; 12450</t>
+          <t>932; 11005</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9466; 24376</t>
+          <t>8713; 24797</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8031; 22925</t>
+          <t>8087; 22964</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2584; 14549</t>
+          <t>2778; 15100</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4495; 18744</t>
+          <t>4363; 18357</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4935; 19043</t>
+          <t>5049; 19489</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14860; 33867</t>
+          <t>14862; 33564</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4882; 16598</t>
+          <t>4951; 17750</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7620; 23176</t>
+          <t>7072; 21966</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10964; 27106</t>
+          <t>11150; 28049</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11522; 29098</t>
+          <t>11648; 28665</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14693; 35877</t>
+          <t>14875; 34653</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30017; 54396</t>
+          <t>28892; 54378</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2539; 12534</t>
+          <t>2524; 12943</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1012; 8298</t>
+          <t>989; 8337</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1730; 10315</t>
+          <t>1907; 10663</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1877; 11464</t>
+          <t>1910; 10864</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>982; 10918</t>
+          <t>979; 11502</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2918; 12853</t>
+          <t>2815; 13109</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6026; 19052</t>
+          <t>5509; 18997</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2999; 14757</t>
+          <t>2714; 13831</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6442; 19219</t>
+          <t>6450; 18551</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1033; 9689</t>
+          <t>1035; 9563</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>975; 9837</t>
+          <t>970; 8949</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 7233</t>
+          <t>0; 6013</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1907; 11146</t>
+          <t>2127; 12761</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3924; 17033</t>
+          <t>3903; 16657</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1921; 12055</t>
+          <t>1886; 12235</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4293; 16525</t>
+          <t>4311; 17243</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6894; 21540</t>
+          <t>6805; 21282</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2985; 14404</t>
+          <t>3356; 15838</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5845; 19605</t>
+          <t>5577; 19600</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7746; 23143</t>
+          <t>7699; 23964</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4359; 19559</t>
+          <t>4500; 19365</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14907; 34536</t>
+          <t>15473; 35473</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7668; 22896</t>
+          <t>6945; 21965</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8039; 24185</t>
+          <t>7860; 23174</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24193; 47937</t>
+          <t>24181; 47454</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>17769; 38629</t>
+          <t>18130; 40435</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15766; 35659</t>
+          <t>15798; 36689</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6400; 19158</t>
+          <t>5892; 19405</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1991; 13410</t>
+          <t>1042; 12076</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6925; 21959</t>
+          <t>7197; 21483</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4572; 17986</t>
+          <t>4540; 19078</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3636; 15605</t>
+          <t>3766; 16550</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5308; 20321</t>
+          <t>5399; 19361</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12922; 32037</t>
+          <t>13270; 33452</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7284; 22811</t>
+          <t>7397; 23777</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15823; 36869</t>
+          <t>15238; 35765</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>49747; 80395</t>
+          <t>49811; 80461</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>35840; 65963</t>
+          <t>34584; 63186</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>61151; 96900</t>
+          <t>61511; 96961</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>69534; 106829</t>
+          <t>68707; 105070</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>68765; 106697</t>
+          <t>66714; 105433</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>59388; 95811</t>
+          <t>59852; 96283</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>126092; 178096</t>
+          <t>127168; 175380</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>114248; 163248</t>
+          <t>111290; 159439</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>128980; 177268</t>
+          <t>130042; 179356</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C09-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C09-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,51</t>
+          <t>0,91; 5,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,56</t>
+          <t>0,47; 5,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 8,14</t>
+          <t>2,32; 7,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 7,12</t>
+          <t>1,21; 6,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 12,11</t>
+          <t>4,44; 11,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 8,15</t>
+          <t>2,4; 9,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,3</t>
+          <t>1,49; 5,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,26</t>
+          <t>2,86; 7,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,67</t>
+          <t>2,89; 6,63</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,74</t>
+          <t>1,73; 5,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,83</t>
+          <t>0,49; 2,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,74</t>
+          <t>1,32; 4,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,54</t>
+          <t>1,99; 5,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,16</t>
+          <t>1,02; 4,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,02</t>
+          <t>0,52; 2,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,94</t>
+          <t>2,22; 4,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,03</t>
+          <t>1,0; 3,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,27</t>
+          <t>1,14; 3,42</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,34</t>
+          <t>0,75; 4,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,14</t>
+          <t>0,34; 3,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,02</t>
+          <t>0,27; 2,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,73</t>
+          <t>2,11; 6,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,15</t>
+          <t>1,3; 5,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,58</t>
+          <t>0,3; 3,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,72</t>
+          <t>1,81; 4,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,7</t>
+          <t>1,31; 3,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,52</t>
+          <t>0,47; 2,59</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,86</t>
+          <t>1,6; 6,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,35</t>
+          <t>1,57; 6,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 10,17</t>
+          <t>4,52; 10,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,93</t>
+          <t>1,6; 5,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,45</t>
+          <t>2,15; 6,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 8,04</t>
+          <t>3,09; 7,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,05</t>
+          <t>2,01; 5,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,35</t>
+          <t>2,32; 5,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 8,01</t>
+          <t>4,46; 8,22</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 7,6</t>
+          <t>1,48; 7,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,29</t>
+          <t>0,64; 5,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 8,94</t>
+          <t>1,5; 8,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,25</t>
+          <t>1,04; 6,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,9</t>
+          <t>0,58; 6,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 9,01</t>
+          <t>2,02; 8,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,52</t>
+          <t>1,55; 5,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,27</t>
+          <t>0,64; 4,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,01</t>
+          <t>2,46; 7,48</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,05</t>
+          <t>0,55; 4,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,59</t>
+          <t>0,4; 3,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 6,24</t>
+          <t>0,96; 5,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,29</t>
+          <t>1,54; 6,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,95</t>
+          <t>0,76; 5,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,38</t>
+          <t>1,1; 4,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,14</t>
+          <t>1,34; 4,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,29</t>
+          <t>0,61; 3,05</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,22</t>
+          <t>1,18; 4,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,17</t>
+          <t>1,23; 4,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,38</t>
+          <t>1,03; 4,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,58</t>
+          <t>2,83; 6,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,51</t>
+          <t>1,23; 3,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,76</t>
+          <t>1,63; 4,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,73</t>
+          <t>2,41; 4,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,37</t>
+          <t>1,54; 3,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,95</t>
+          <t>1,75; 3,94</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,71</t>
+          <t>1,17; 3,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,97</t>
+          <t>0,33; 2,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,36</t>
+          <t>1,1; 3,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,24</t>
+          <t>0,88; 3,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,42</t>
+          <t>0,61; 2,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,8</t>
+          <t>0,66; 2,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,01</t>
+          <t>1,23; 2,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,84</t>
+          <t>0,57; 1,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,69</t>
+          <t>1,13; 2,78</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,28</t>
+          <t>2,03; 3,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,23</t>
+          <t>1,3; 2,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,64</t>
+          <t>2,26; 3,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,84</t>
+          <t>2,54; 3,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,43</t>
+          <t>2,25; 3,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,36</t>
+          <t>2,13; 3,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,38</t>
+          <t>2,44; 3,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,7</t>
+          <t>1,88; 2,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,24</t>
+          <t>2,36; 3,27</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1688; 10549</t>
+          <t>1749; 9946</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>939; 11396</t>
+          <t>1164; 13820</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6230; 19968</t>
+          <t>5680; 19567</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2234; 14329</t>
+          <t>2434; 13277</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10847; 30189</t>
+          <t>11073; 29718</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5773; 20074</t>
+          <t>5901; 22599</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6219; 20824</t>
+          <t>5846; 19867</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14315; 36219</t>
+          <t>14287; 36888</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14464; 32787</t>
+          <t>14197; 32571</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7229; 23442</t>
+          <t>7060; 22983</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1939; 11174</t>
+          <t>1946; 10183</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4493; 17209</t>
+          <t>4794; 17523</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8902; 24459</t>
+          <t>8782; 23864</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4075; 17146</t>
+          <t>4209; 18283</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2010; 11877</t>
+          <t>2060; 11717</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19679; 41960</t>
+          <t>18898; 40003</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7899; 24413</t>
+          <t>8091; 25034</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8824; 24700</t>
+          <t>8617; 25869</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1754; 10273</t>
+          <t>1785; 10243</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1009; 9201</t>
+          <t>1004; 10097</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>783; 8781</t>
+          <t>782; 8147</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5920; 19427</t>
+          <t>6082; 19707</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4282; 16941</t>
+          <t>4270; 17052</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>932; 11005</t>
+          <t>925; 11994</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8713; 24797</t>
+          <t>9517; 24584</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8087; 22964</t>
+          <t>8121; 22672</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2778; 15100</t>
+          <t>2823; 15512</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4363; 18357</t>
+          <t>4280; 17794</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5049; 19489</t>
+          <t>4832; 18973</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14862; 33564</t>
+          <t>14910; 33204</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4951; 17750</t>
+          <t>4798; 16863</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7072; 21966</t>
+          <t>7309; 22895</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11150; 28049</t>
+          <t>10797; 27763</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11648; 28665</t>
+          <t>11381; 29058</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14875; 34653</t>
+          <t>15035; 36267</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28892; 54378</t>
+          <t>30293; 55838</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2524; 12943</t>
+          <t>2526; 13534</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>989; 8337</t>
+          <t>1013; 8309</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1907; 10663</t>
+          <t>1786; 10343</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1910; 10864</t>
+          <t>1817; 10708</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>979; 11502</t>
+          <t>962; 10929</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2815; 13109</t>
+          <t>2946; 12817</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5509; 18997</t>
+          <t>5352; 19036</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2714; 13831</t>
+          <t>2087; 14047</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6450; 18551</t>
+          <t>6505; 19793</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1035; 9563</t>
+          <t>1035; 9382</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>970; 8949</t>
+          <t>985; 9667</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6013</t>
+          <t>0; 6902</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2127; 12761</t>
+          <t>1970; 11698</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3903; 16657</t>
+          <t>4077; 17901</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1886; 12235</t>
+          <t>1891; 12593</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4311; 17243</t>
+          <t>4350; 17836</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6805; 21282</t>
+          <t>6861; 22471</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3356; 15838</t>
+          <t>2944; 14673</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5577; 19600</t>
+          <t>5486; 19309</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7699; 23964</t>
+          <t>7055; 22944</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4500; 19365</t>
+          <t>4564; 19386</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15473; 35473</t>
+          <t>15275; 34978</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6945; 21965</t>
+          <t>7687; 23157</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7860; 23174</t>
+          <t>7924; 24211</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24181; 47454</t>
+          <t>24230; 47557</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18130; 40435</t>
+          <t>18469; 39525</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15798; 36689</t>
+          <t>16247; 36581</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5892; 19405</t>
+          <t>6113; 18911</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1042; 12076</t>
+          <t>1993; 13037</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7197; 21483</t>
+          <t>7050; 21282</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4540; 19078</t>
+          <t>5206; 18731</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3766; 16550</t>
+          <t>4136; 16658</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5399; 19361</t>
+          <t>4545; 19285</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13270; 33452</t>
+          <t>13661; 31804</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7397; 23777</t>
+          <t>7329; 24961</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15238; 35765</t>
+          <t>15000; 37071</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>49811; 80461</t>
+          <t>49727; 81908</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>34584; 63186</t>
+          <t>36997; 66974</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>61511; 96961</t>
+          <t>60098; 94125</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>68707; 105070</t>
+          <t>69568; 105202</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>66714; 105433</t>
+          <t>69078; 106971</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>59852; 96283</t>
+          <t>61045; 97964</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>127168; 175380</t>
+          <t>126470; 175335</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>111290; 159439</t>
+          <t>111187; 160618</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>130042; 179356</t>
+          <t>130383; 180676</t>
         </is>
       </c>
     </row>
